--- a/authorization_forms/044_volunteer_authorization_and_consent_form--authorization_forms.xlsx
+++ b/authorization_forms/044_volunteer_authorization_and_consent_form--authorization_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -619,8 +619,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,12 +648,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'street',_'name':_'street',_'type':_'text',_'required':_true}</t>
+          <t>street</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'street', 'name': 'street', 'type': 'text', 'required': True}</t>
+          <t>street</t>
         </is>
       </c>
     </row>
@@ -665,12 +665,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'city',_'name':_'city',_'type':_'text',_'required':_true}</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'city', 'name': 'city', 'type': 'text', 'required': True}</t>
+          <t>city</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'state',_'name':_'state',_'type':_'select_one',_'options':_['address',_'address',_'address']}</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'state', 'name': 'state', 'type': 'select_one', 'options': ['address', 'address', 'address']}</t>
+          <t>state</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'name',_'name':_'name',_'type':_'text',_'required':_true}</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'name', 'name': 'name', 'type': 'text', 'required': True}</t>
+          <t>name</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email',_'name':_'email',_'type':_'email',_'required':_true}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'email', 'name': 'email', 'type': 'email', 'required': True}</t>
+          <t>email</t>
         </is>
       </c>
     </row>
@@ -733,12 +733,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'phone',_'name':_'phone',_'type':_'phone',_'required':_true}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'phone', 'name': 'phone', 'type': 'phone', 'required': True}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'role',_'name':_'role',_'type':_'select_multiple',_'options':_['volunteer',_'volunteer',_'volunteer']}</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'role', 'name': 'role', 'type': 'select_multiple', 'options': ['Volunteer', 'Volunteer', 'Volunteer']}</t>
+          <t>role</t>
         </is>
       </c>
     </row>
@@ -767,12 +767,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'date',_'name':_'date',_'type':_'date'}</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'date', 'name': 'date', 'type': 'date'}</t>
+          <t>date</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'time',_'name':_'time',_'type':_'time',_'required':_true}</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'time', 'name': 'time', 'type': 'time', 'required': True}</t>
+          <t>time</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'location',_'name':_'location',_'type':_'text',_'required':_true}</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'location', 'name': 'location', 'type': 'text', 'required': True}</t>
+          <t>location</t>
         </is>
       </c>
     </row>
